--- a/AAII_Financials/Yearly/CAT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CAT_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>CAT</t>
   </si>
@@ -656,198 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>67060000</v>
+      </c>
+      <c r="E8" s="3">
         <v>59427000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>50971000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>41748000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>53800000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>54722000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>45462000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>38537000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>47011000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>55184000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>55656000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>65875000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>60138000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>42657000</v>
+      </c>
+      <c r="E9" s="3">
         <v>41135000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>35454000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>29039000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>36508000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>36815000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>31087000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>27782000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>33284000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>80485000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>41455000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>47851000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>44402000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>24403000</v>
+      </c>
+      <c r="E10" s="3">
         <v>18292000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15517000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12709000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>17292000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>17907000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14375000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10755000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13727000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-25301000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14201000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18024000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15736000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,50 +876,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2108000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1814000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1686000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1415000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1693000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1850000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1842000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1853000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2119000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2380000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2046000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2466000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2297000</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -947,51 +963,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>780000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1224000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>90000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>354000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>266000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>386000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1171000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1614000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1551000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>430000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>242000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>676000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>117000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1031,9 +1053,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1047,92 +1072,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>54094000</v>
+      </c>
+      <c r="E17" s="3">
         <v>51523000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>44093000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>37195000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>45510000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>46429000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>40917000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>37375000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43226000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>51870000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>50029000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>57304000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>52990000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>12966000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7904000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6878000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4553000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8290000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8293000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4545000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1162000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3785000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3314000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5627000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8571000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7148000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1149,218 +1181,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>595000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1291000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1814000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-44000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-57000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-67000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>68000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-518000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>161000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>322000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-34000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>132000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-27000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>15705000</v>
+      </c>
+      <c r="E21" s="3">
         <v>11414000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11044000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6941000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10810000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10992000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7490000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3678000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6992000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6799000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8680000</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9648000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>511000</v>
+      </c>
+      <c r="E22" s="3">
         <v>443000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>488000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>514000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>421000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>404000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>531000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>505000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>507000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>484000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>465000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>467000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>396000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>13050000</v>
+      </c>
+      <c r="E23" s="3">
         <v>8752000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8204000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3995000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7812000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7822000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4082000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>139000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3439000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3152000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5128000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8236000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6725000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2781000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2067000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1778000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1086000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1924000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1802000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>968000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>192000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>916000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>692000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1319000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2528000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1720000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1400,93 +1448,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>10269000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6685000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6426000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2909000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5888000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6020000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3114000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-53000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2523000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2460000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3809000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5708000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5005000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>10335000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6705000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6453000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2918000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5915000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6043000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3125000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-67000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2512000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2452000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3789000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5681000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4928000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1526,32 +1583,35 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="3">
         <v>36000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>80000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>178000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>104000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-2371000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
@@ -1568,9 +1628,12 @@
       <c r="O29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1610,9 +1673,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1652,93 +1718,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-595000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1291000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1814000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>44000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>57000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>67000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-68000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>518000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-161000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-322000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>34000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-132000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>27000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10335000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6705000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6489000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2998000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6093000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6147000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>754000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-67000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2512000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2452000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3789000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5681000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4928000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1778,98 +1853,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10335000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6705000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6489000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2998000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6093000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6147000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>754000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-67000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2512000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2452000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3789000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5681000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4928000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1886,8 +1970,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1904,50 +1989,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6978000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7004000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9254000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9352000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8284000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7857000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8261000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7168000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6460000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7341000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6081000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5490000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3057000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1960,14 +2049,14 @@
       <c r="F42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
+      <c r="G42" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>1000</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>24</v>
@@ -1978,312 +2067,336 @@
       <c r="L42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M42" s="3">
+      <c r="M42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N42" s="3">
         <v>14000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>29000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>22000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18820000</v>
+      </c>
+      <c r="E43" s="3">
         <v>17869000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17375000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>16780000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17820000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>17417000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16133000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14441000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15668000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16726000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>17089000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8831000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>25599000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16565000</v>
+      </c>
+      <c r="E44" s="3">
         <v>16270000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14038000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>11402000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11266000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11529000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10018000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8614000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9700000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12205000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12625000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>15547000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>14544000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4586000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2642000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2788000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1930000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1823000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1799000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1832000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1744000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3206000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2595000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2526000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12241000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12631000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>46949000</v>
+      </c>
+      <c r="E46" s="3">
         <v>43785000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>43455000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>39464000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>39193000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>38603000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>36244000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>31967000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>33508000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>38867000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>38335000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>42138000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>37900000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13902000</v>
+      </c>
+      <c r="E47" s="3">
         <v>13278000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>13911000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13407000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13812000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14444000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14768000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>14830000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14980000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>16175000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>17868000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>30753000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>26037000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13236000</v>
+      </c>
+      <c r="E48" s="3">
         <v>12592000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12715000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13004000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13528000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13574000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14155000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15322000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32180000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16577000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34150000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16461000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14395000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5872000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6046000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7366000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7702000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7761000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8114000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8311000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8369000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9436000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9770000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10552000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10958000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10912000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2323,9 +2436,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2365,51 +2481,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7517000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6242000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5346000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4747000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4159000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3774000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3484000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4216000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6326000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3292000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2463000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4005000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4516000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2449,51 +2571,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>87476000</v>
+      </c>
+      <c r="E54" s="3">
         <v>81943000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>82793000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>78324000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78453000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78509000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>76962000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>74704000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>78342000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>84681000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>84896000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>88970000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>81218000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2510,8 +2638,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2528,260 +2657,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7906000</v>
+      </c>
+      <c r="E57" s="3">
         <v>8689000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8154000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6128000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5957000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7051000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6487000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4614000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5023000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6515000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6560000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6753000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8161000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13406000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11279000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11756000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11164000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11376000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11553000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11031000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13965000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12844000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11501000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11031000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12391000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9648000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13416000</v>
+      </c>
+      <c r="E59" s="3">
         <v>11563000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9937000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8425000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9288000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9614000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9413000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7553000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11491000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9861000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9706000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10271000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16344000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34728000</v>
+      </c>
+      <c r="E60" s="3">
         <v>31531000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29847000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>25717000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>26621000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28218000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26931000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26132000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26242000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27877000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27297000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>29415000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28357000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>24472000</v>
+      </c>
+      <c r="E61" s="3">
         <v>25714000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>26033000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25999000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>26281000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>25000000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23847000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22818000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25169000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27784000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26719000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27752000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>24944000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8773000</v>
+      </c>
+      <c r="E62" s="3">
         <v>8807000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10397000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11230000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10922000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11211000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12418000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12541000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12046000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12194000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13031000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14221000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18098000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2821,9 +2969,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2863,9 +3014,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2905,51 +3059,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67982000</v>
+      </c>
+      <c r="E66" s="3">
         <v>66074000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>66309000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>62993000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>63865000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>64470000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>63265000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>61567000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>63533000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>67935000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>64085000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>71438000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>68335000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2966,8 +3126,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3007,9 +3168,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3049,9 +3213,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3091,9 +3258,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3133,51 +3303,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>51250000</v>
+      </c>
+      <c r="E72" s="3">
         <v>43514000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>39282000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>35167000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>34437000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>30427000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>26301000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>27377000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>29246000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>33887000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>31854000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>29558000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>25219000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3217,9 +3393,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3259,9 +3438,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3301,51 +3483,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19494000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15869000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16484000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15331000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14588000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14039000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13697000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13137000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14809000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16746000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20811000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17532000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12883000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3385,98 +3573,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10335000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6705000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6489000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2998000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6093000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6147000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>754000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-67000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2512000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2452000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3789000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5681000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4928000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3493,50 +3690,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2144000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2219000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2352000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2432000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2577000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2766000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2877000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3034000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3046000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3163000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3087000</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2527000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3576,9 +3777,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3618,9 +3822,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3660,9 +3867,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3702,9 +3912,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3744,51 +3957,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12885000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7766000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7198000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6327000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6912000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6558000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5706000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5639000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6699000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8057000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10191000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5184000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6957000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3805,50 +4024,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3092000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2599000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2472000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2115000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2669000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2916000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2336000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2928000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3261000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3379000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4446000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5076000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3924000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3888,9 +4111,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3930,51 +4156,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5871000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2541000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3084000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1485000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1928000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3212000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-966000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1780000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3517000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3627000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5046000</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11427000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3991,50 +4223,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-2563000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-2440000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2332000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2243000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-2132000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-1951000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-1831000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-1799000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1757000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1620000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1111000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1617000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1159000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4074,9 +4310,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4116,9 +4355,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4158,133 +4400,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6932000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7281000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4188000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3755000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4538000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3650000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3657000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3894000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2996000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4511000</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4019000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-194000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-29000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-13000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-44000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-126000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>38000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-28000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-169000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-174000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-43000</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="O101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-84000</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2250000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-103000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1074000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>402000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-430000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1121000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>688000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-881000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1260000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>591000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2433000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-535000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CAT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CAT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>CAT</t>
   </si>
@@ -774,25 +774,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>42657000</v>
+        <v>42767000</v>
       </c>
       <c r="E9" s="3">
-        <v>41135000</v>
+        <v>41350000</v>
       </c>
       <c r="F9" s="3">
-        <v>35454000</v>
+        <v>35513000</v>
       </c>
       <c r="G9" s="3">
-        <v>29039000</v>
+        <v>29082000</v>
       </c>
       <c r="H9" s="3">
-        <v>36508000</v>
+        <v>36630000</v>
       </c>
       <c r="I9" s="3">
-        <v>36815000</v>
+        <v>36997000</v>
       </c>
       <c r="J9" s="3">
-        <v>31087000</v>
+        <v>31260000</v>
       </c>
       <c r="K9" s="3">
         <v>27782000</v>
@@ -819,25 +819,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>24403000</v>
+        <v>21275000</v>
       </c>
       <c r="E10" s="3">
-        <v>18292000</v>
+        <v>15565000</v>
       </c>
       <c r="F10" s="3">
-        <v>15517000</v>
+        <v>13189000</v>
       </c>
       <c r="G10" s="3">
-        <v>12709000</v>
+        <v>10127000</v>
       </c>
       <c r="H10" s="3">
-        <v>17292000</v>
+        <v>14462000</v>
       </c>
       <c r="I10" s="3">
-        <v>17907000</v>
+        <v>14903000</v>
       </c>
       <c r="J10" s="3">
-        <v>14375000</v>
+        <v>11824000</v>
       </c>
       <c r="K10" s="3">
         <v>10755000</v>
@@ -973,25 +973,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>780000</v>
+        <v>660000</v>
       </c>
       <c r="E14" s="3">
-        <v>1224000</v>
+        <v>1066000</v>
       </c>
       <c r="F14" s="3">
-        <v>90000</v>
+        <v>-104000</v>
       </c>
       <c r="G14" s="3">
-        <v>354000</v>
+        <v>303000</v>
       </c>
       <c r="H14" s="3">
-        <v>266000</v>
+        <v>41000</v>
       </c>
       <c r="I14" s="3">
-        <v>386000</v>
+        <v>206000</v>
       </c>
       <c r="J14" s="3">
-        <v>1171000</v>
+        <v>891000</v>
       </c>
       <c r="K14" s="3">
         <v>1614000</v>
@@ -1018,25 +1018,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2069000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2219000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2352000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>2432000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2577000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>2766000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2877000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1079,25 +1079,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>54094000</v>
+        <v>53393000</v>
       </c>
       <c r="E17" s="3">
-        <v>51523000</v>
+        <v>49672000</v>
       </c>
       <c r="F17" s="3">
-        <v>44093000</v>
+        <v>42696000</v>
       </c>
       <c r="G17" s="3">
-        <v>37195000</v>
+        <v>36913000</v>
       </c>
       <c r="H17" s="3">
-        <v>45510000</v>
+        <v>45687000</v>
       </c>
       <c r="I17" s="3">
-        <v>46429000</v>
+        <v>46386000</v>
       </c>
       <c r="J17" s="3">
-        <v>40917000</v>
+        <v>39886000</v>
       </c>
       <c r="K17" s="3">
         <v>37375000</v>
@@ -1124,25 +1124,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>12966000</v>
+        <v>13667000</v>
       </c>
       <c r="E18" s="3">
-        <v>7904000</v>
+        <v>9755000</v>
       </c>
       <c r="F18" s="3">
-        <v>6878000</v>
+        <v>8275000</v>
       </c>
       <c r="G18" s="3">
-        <v>4553000</v>
+        <v>4835000</v>
       </c>
       <c r="H18" s="3">
-        <v>8290000</v>
+        <v>8113000</v>
       </c>
       <c r="I18" s="3">
-        <v>8293000</v>
+        <v>8336000</v>
       </c>
       <c r="J18" s="3">
-        <v>4545000</v>
+        <v>5576000</v>
       </c>
       <c r="K18" s="3">
         <v>1162000</v>
@@ -1188,25 +1188,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>595000</v>
+        <v>-123000</v>
       </c>
       <c r="E20" s="3">
-        <v>1291000</v>
+        <v>-358000</v>
       </c>
       <c r="F20" s="3">
-        <v>1814000</v>
+        <v>-264000</v>
       </c>
       <c r="G20" s="3">
-        <v>-44000</v>
+        <v>121000</v>
       </c>
       <c r="H20" s="3">
-        <v>-57000</v>
+        <v>13000</v>
       </c>
       <c r="I20" s="3">
-        <v>-67000</v>
+        <v>75000</v>
       </c>
       <c r="J20" s="3">
-        <v>68000</v>
+        <v>178000</v>
       </c>
       <c r="K20" s="3">
         <v>-518000</v>
@@ -1233,25 +1233,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>15705000</v>
+        <v>15859000</v>
       </c>
       <c r="E21" s="3">
-        <v>11414000</v>
+        <v>12332000</v>
       </c>
       <c r="F21" s="3">
-        <v>11044000</v>
+        <v>10891000</v>
       </c>
       <c r="G21" s="3">
-        <v>6941000</v>
+        <v>7146000</v>
       </c>
       <c r="H21" s="3">
-        <v>10810000</v>
+        <v>10677000</v>
       </c>
       <c r="I21" s="3">
-        <v>10992000</v>
+        <v>11027000</v>
       </c>
       <c r="J21" s="3">
-        <v>7490000</v>
+        <v>8275000</v>
       </c>
       <c r="K21" s="3">
         <v>3678000</v>
@@ -1323,25 +1323,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>13050000</v>
+        <v>13113000</v>
       </c>
       <c r="E23" s="3">
-        <v>8752000</v>
+        <v>8771000</v>
       </c>
       <c r="F23" s="3">
-        <v>8204000</v>
+        <v>8235000</v>
       </c>
       <c r="G23" s="3">
-        <v>3995000</v>
+        <v>4009000</v>
       </c>
       <c r="H23" s="3">
-        <v>7812000</v>
+        <v>7840000</v>
       </c>
       <c r="I23" s="3">
-        <v>7822000</v>
+        <v>7846000</v>
       </c>
       <c r="J23" s="3">
-        <v>4082000</v>
+        <v>4098000</v>
       </c>
       <c r="K23" s="3">
         <v>139000</v>
@@ -1374,19 +1374,19 @@
         <v>2067000</v>
       </c>
       <c r="F24" s="3">
-        <v>1778000</v>
+        <v>1742000</v>
       </c>
       <c r="G24" s="3">
-        <v>1086000</v>
+        <v>1006000</v>
       </c>
       <c r="H24" s="3">
-        <v>1924000</v>
+        <v>1746000</v>
       </c>
       <c r="I24" s="3">
-        <v>1802000</v>
+        <v>1698000</v>
       </c>
       <c r="J24" s="3">
-        <v>968000</v>
+        <v>3339000</v>
       </c>
       <c r="K24" s="3">
         <v>192000</v>
@@ -1458,25 +1458,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>10269000</v>
+        <v>10332000</v>
       </c>
       <c r="E26" s="3">
-        <v>6685000</v>
+        <v>6704000</v>
       </c>
       <c r="F26" s="3">
-        <v>6426000</v>
+        <v>6493000</v>
       </c>
       <c r="G26" s="3">
-        <v>2909000</v>
+        <v>3003000</v>
       </c>
       <c r="H26" s="3">
-        <v>5888000</v>
+        <v>6094000</v>
       </c>
       <c r="I26" s="3">
-        <v>6020000</v>
+        <v>6148000</v>
       </c>
       <c r="J26" s="3">
-        <v>3114000</v>
+        <v>759000</v>
       </c>
       <c r="K26" s="3">
         <v>-53000</v>
@@ -1509,19 +1509,19 @@
         <v>6705000</v>
       </c>
       <c r="F27" s="3">
-        <v>6453000</v>
+        <v>6489000</v>
       </c>
       <c r="G27" s="3">
-        <v>2918000</v>
+        <v>2998000</v>
       </c>
       <c r="H27" s="3">
-        <v>5915000</v>
+        <v>6093000</v>
       </c>
       <c r="I27" s="3">
-        <v>6043000</v>
+        <v>6147000</v>
       </c>
       <c r="J27" s="3">
-        <v>3125000</v>
+        <v>754000</v>
       </c>
       <c r="K27" s="3">
         <v>-67000</v>
@@ -1592,26 +1592,26 @@
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>24</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>178000</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>104000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-2371000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
@@ -1728,25 +1728,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-595000</v>
+        <v>123000</v>
       </c>
       <c r="E32" s="3">
-        <v>-1291000</v>
+        <v>358000</v>
       </c>
       <c r="F32" s="3">
-        <v>-1814000</v>
+        <v>264000</v>
       </c>
       <c r="G32" s="3">
-        <v>44000</v>
+        <v>-121000</v>
       </c>
       <c r="H32" s="3">
-        <v>57000</v>
+        <v>-13000</v>
       </c>
       <c r="I32" s="3">
-        <v>67000</v>
+        <v>-75000</v>
       </c>
       <c r="J32" s="3">
-        <v>-68000</v>
+        <v>-178000</v>
       </c>
       <c r="K32" s="3">
         <v>518000</v>
@@ -1996,25 +1996,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6978000</v>
+        <v>6106000</v>
       </c>
       <c r="E41" s="3">
-        <v>7004000</v>
+        <v>6042000</v>
       </c>
       <c r="F41" s="3">
-        <v>9254000</v>
+        <v>8428000</v>
       </c>
       <c r="G41" s="3">
-        <v>9352000</v>
+        <v>8822000</v>
       </c>
       <c r="H41" s="3">
-        <v>8284000</v>
+        <v>7299000</v>
       </c>
       <c r="I41" s="3">
-        <v>7857000</v>
+        <v>6968000</v>
       </c>
       <c r="J41" s="3">
-        <v>8261000</v>
+        <v>7381000</v>
       </c>
       <c r="K41" s="3">
         <v>7168000</v>
@@ -2040,26 +2040,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>24</v>
+      <c r="D42" s="3">
+        <v>1900000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>964000</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>24</v>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>24</v>
@@ -2086,25 +2086,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>18820000</v>
+        <v>9556000</v>
       </c>
       <c r="E43" s="3">
-        <v>17869000</v>
+        <v>9103000</v>
       </c>
       <c r="F43" s="3">
-        <v>17375000</v>
+        <v>8664000</v>
       </c>
       <c r="G43" s="3">
-        <v>16780000</v>
+        <v>7178000</v>
       </c>
       <c r="H43" s="3">
-        <v>17820000</v>
+        <v>8484000</v>
       </c>
       <c r="I43" s="3">
-        <v>17417000</v>
+        <v>8714000</v>
       </c>
       <c r="J43" s="3">
-        <v>16133000</v>
+        <v>7376000</v>
       </c>
       <c r="K43" s="3">
         <v>14441000</v>
@@ -2175,26 +2175,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>4586000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2642000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2788000</v>
+      <c r="D45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="G45" s="3">
-        <v>1930000</v>
+        <v>119000</v>
       </c>
       <c r="H45" s="3">
-        <v>1823000</v>
+        <v>23000</v>
       </c>
       <c r="I45" s="3">
-        <v>1799000</v>
+        <v>19000</v>
       </c>
       <c r="J45" s="3">
-        <v>1832000</v>
+        <v>48000</v>
       </c>
       <c r="K45" s="3">
         <v>1744000</v>
@@ -2265,26 +2265,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>13902000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>13278000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>13911000</v>
+      <c r="D47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="G47" s="3">
-        <v>13407000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>13812000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>14444000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>14768000</v>
+        <v>4000</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K47" s="3">
         <v>14830000</v>
@@ -2311,25 +2311,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13236000</v>
+        <v>9250000</v>
       </c>
       <c r="E48" s="3">
-        <v>12592000</v>
+        <v>8750000</v>
       </c>
       <c r="F48" s="3">
-        <v>12715000</v>
+        <v>8797000</v>
       </c>
       <c r="G48" s="3">
-        <v>13004000</v>
+        <v>8912000</v>
       </c>
       <c r="H48" s="3">
-        <v>13528000</v>
+        <v>9230000</v>
       </c>
       <c r="I48" s="3">
-        <v>13574000</v>
+        <v>9085000</v>
       </c>
       <c r="J48" s="3">
-        <v>14155000</v>
+        <v>9823000</v>
       </c>
       <c r="K48" s="3">
         <v>15322000</v>
@@ -2374,7 +2374,7 @@
         <v>8114000</v>
       </c>
       <c r="J49" s="3">
-        <v>8311000</v>
+        <v>8289000</v>
       </c>
       <c r="K49" s="3">
         <v>8369000</v>
@@ -2491,25 +2491,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7517000</v>
+        <v>4883000</v>
       </c>
       <c r="E52" s="3">
-        <v>6242000</v>
+        <v>4195000</v>
       </c>
       <c r="F52" s="3">
-        <v>5346000</v>
+        <v>3677000</v>
       </c>
       <c r="G52" s="3">
-        <v>4747000</v>
+        <v>3462000</v>
       </c>
       <c r="H52" s="3">
-        <v>4159000</v>
+        <v>2812000</v>
       </c>
       <c r="I52" s="3">
-        <v>3774000</v>
+        <v>962000</v>
       </c>
       <c r="J52" s="3">
-        <v>3484000</v>
+        <v>950000</v>
       </c>
       <c r="K52" s="3">
         <v>4216000</v>
@@ -2709,25 +2709,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>13406000</v>
+        <v>13553000</v>
       </c>
       <c r="E58" s="3">
-        <v>11279000</v>
+        <v>11430000</v>
       </c>
       <c r="F58" s="3">
-        <v>11756000</v>
+        <v>11914000</v>
       </c>
       <c r="G58" s="3">
-        <v>11164000</v>
+        <v>11332000</v>
       </c>
       <c r="H58" s="3">
-        <v>11376000</v>
+        <v>11574000</v>
       </c>
       <c r="I58" s="3">
-        <v>11553000</v>
+        <v>11593000</v>
       </c>
       <c r="J58" s="3">
-        <v>11031000</v>
+        <v>11033000</v>
       </c>
       <c r="K58" s="3">
         <v>13965000</v>
@@ -2754,25 +2754,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13416000</v>
+        <v>5554000</v>
       </c>
       <c r="E59" s="3">
-        <v>11563000</v>
+        <v>5019000</v>
       </c>
       <c r="F59" s="3">
-        <v>9937000</v>
+        <v>3779000</v>
       </c>
       <c r="G59" s="3">
-        <v>8425000</v>
+        <v>3561000</v>
       </c>
       <c r="H59" s="3">
-        <v>9288000</v>
+        <v>3757000</v>
       </c>
       <c r="I59" s="3">
-        <v>9614000</v>
+        <v>3735000</v>
       </c>
       <c r="J59" s="3">
-        <v>9413000</v>
+        <v>3657000</v>
       </c>
       <c r="K59" s="3">
         <v>7553000</v>
@@ -2844,25 +2844,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>24472000</v>
+        <v>9006000</v>
       </c>
       <c r="E61" s="3">
-        <v>25714000</v>
+        <v>9926000</v>
       </c>
       <c r="F61" s="3">
-        <v>26033000</v>
+        <v>10230000</v>
       </c>
       <c r="G61" s="3">
-        <v>25999000</v>
+        <v>10206000</v>
       </c>
       <c r="H61" s="3">
-        <v>26281000</v>
+        <v>9602000</v>
       </c>
       <c r="I61" s="3">
-        <v>25000000</v>
+        <v>8005000</v>
       </c>
       <c r="J61" s="3">
-        <v>23847000</v>
+        <v>7929000</v>
       </c>
       <c r="K61" s="3">
         <v>22818000</v>
@@ -2889,25 +2889,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8773000</v>
+        <v>3334000</v>
       </c>
       <c r="E62" s="3">
-        <v>8807000</v>
+        <v>3251000</v>
       </c>
       <c r="F62" s="3">
-        <v>10397000</v>
+        <v>3909000</v>
       </c>
       <c r="G62" s="3">
-        <v>11230000</v>
+        <v>3065000</v>
       </c>
       <c r="H62" s="3">
-        <v>10922000</v>
+        <v>2981000</v>
       </c>
       <c r="I62" s="3">
-        <v>11211000</v>
+        <v>3319000</v>
       </c>
       <c r="J62" s="3">
-        <v>12418000</v>
+        <v>3657000</v>
       </c>
       <c r="K62" s="3">
         <v>12541000</v>
@@ -3069,25 +3069,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>67982000</v>
+        <v>67973000</v>
       </c>
       <c r="E66" s="3">
-        <v>66074000</v>
+        <v>66052000</v>
       </c>
       <c r="F66" s="3">
-        <v>66309000</v>
+        <v>66277000</v>
       </c>
       <c r="G66" s="3">
-        <v>62993000</v>
+        <v>62946000</v>
       </c>
       <c r="H66" s="3">
-        <v>63865000</v>
+        <v>63824000</v>
       </c>
       <c r="I66" s="3">
-        <v>64470000</v>
+        <v>64429000</v>
       </c>
       <c r="J66" s="3">
-        <v>63265000</v>
+        <v>63196000</v>
       </c>
       <c r="K66" s="3">
         <v>61567000</v>
@@ -3697,25 +3697,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2144000</v>
+        <v>1851000</v>
       </c>
       <c r="E83" s="3">
-        <v>2219000</v>
+        <v>1935000</v>
       </c>
       <c r="F83" s="3">
-        <v>2352000</v>
+        <v>2050000</v>
       </c>
       <c r="G83" s="3">
-        <v>2432000</v>
+        <v>2121000</v>
       </c>
       <c r="H83" s="3">
-        <v>2577000</v>
+        <v>2253000</v>
       </c>
       <c r="I83" s="3">
-        <v>2766000</v>
+        <v>2435000</v>
       </c>
       <c r="J83" s="3">
-        <v>2877000</v>
+        <v>2554000</v>
       </c>
       <c r="K83" s="3">
         <v>3034000</v>
@@ -4230,25 +4230,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2563000</v>
+        <v>2563000</v>
       </c>
       <c r="E96" s="3">
-        <v>-2440000</v>
+        <v>2440000</v>
       </c>
       <c r="F96" s="3">
-        <v>-2332000</v>
+        <v>2332000</v>
       </c>
       <c r="G96" s="3">
-        <v>-2243000</v>
+        <v>2243000</v>
       </c>
       <c r="H96" s="3">
-        <v>-2132000</v>
+        <v>2132000</v>
       </c>
       <c r="I96" s="3">
-        <v>-1951000</v>
+        <v>1951000</v>
       </c>
       <c r="J96" s="3">
-        <v>-1831000</v>
+        <v>1831000</v>
       </c>
       <c r="K96" s="3">
         <v>-1799000</v>

--- a/AAII_Financials/Yearly/CAT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CAT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>CAT</t>
   </si>
@@ -656,210 +656,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>64809000</v>
+      </c>
+      <c r="E8" s="3">
         <v>67060000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>59427000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>50971000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>41748000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>53800000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>54722000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>45462000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38537000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>47011000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>55184000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>55656000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>65875000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>60138000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>40199000</v>
+      </c>
+      <c r="E9" s="3">
         <v>42767000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>41350000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>35513000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>29082000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>36630000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36997000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>31260000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>27782000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>33284000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>80485000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>41455000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>47851000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>44402000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>21088000</v>
+      </c>
+      <c r="E10" s="3">
         <v>21275000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15565000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13189000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10127000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>14462000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14903000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11824000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10755000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13727000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-25301000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14201000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18024000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>15736000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -877,53 +889,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2107000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2108000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1814000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1686000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1415000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1693000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1850000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1842000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1853000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2119000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2380000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2046000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2466000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2297000</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -966,81 +982,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>202000</v>
+      </c>
+      <c r="E14" s="3">
         <v>660000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1066000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-104000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>303000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>41000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>206000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>891000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1614000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1551000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>430000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>242000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>676000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>117000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>2069000</v>
+        <v>2083000</v>
       </c>
       <c r="E15" s="3">
+        <v>2144000</v>
+      </c>
+      <c r="F15" s="3">
         <v>2219000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2352000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2432000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2577000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2766000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2877000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1056,9 +1078,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1073,98 +1098,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>53393000</v>
+        <v>51246000</v>
       </c>
       <c r="E17" s="3">
-        <v>49672000</v>
+        <v>53392000</v>
       </c>
       <c r="F17" s="3">
-        <v>42696000</v>
+        <v>49671000</v>
       </c>
       <c r="G17" s="3">
+        <v>42697000</v>
+      </c>
+      <c r="H17" s="3">
         <v>36913000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>45687000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>46386000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>39886000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37375000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>43226000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>51870000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>50029000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>57304000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>52990000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>13667000</v>
+        <v>13563000</v>
       </c>
       <c r="E18" s="3">
-        <v>9755000</v>
+        <v>13668000</v>
       </c>
       <c r="F18" s="3">
-        <v>8275000</v>
+        <v>9756000</v>
       </c>
       <c r="G18" s="3">
+        <v>8274000</v>
+      </c>
+      <c r="H18" s="3">
         <v>4835000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8113000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8336000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5576000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1162000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3785000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3314000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5627000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8571000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7148000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1182,233 +1214,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-123000</v>
+        <v>-86000</v>
       </c>
       <c r="E20" s="3">
-        <v>-358000</v>
+        <v>-122000</v>
       </c>
       <c r="F20" s="3">
-        <v>-264000</v>
+        <v>-357000</v>
       </c>
       <c r="G20" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="H20" s="3">
         <v>121000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>13000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>75000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>178000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-518000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>161000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>322000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-34000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>132000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>15859000</v>
+        <v>15732000</v>
       </c>
       <c r="E21" s="3">
+        <v>15934000</v>
+      </c>
+      <c r="F21" s="3">
         <v>12332000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>10891000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7146000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10677000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11027000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8275000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3678000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6992000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6799000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8680000</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9648000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>512000</v>
+      </c>
+      <c r="E22" s="3">
         <v>511000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>443000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>488000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>514000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>421000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>404000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>531000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>505000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>507000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>484000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>465000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>467000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>396000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>13417000</v>
+      </c>
+      <c r="E23" s="3">
         <v>13113000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8771000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8235000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4009000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7840000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7846000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4098000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>139000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3439000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3152000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5128000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8236000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6725000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2629000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2781000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2067000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1742000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1006000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1746000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1698000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3339000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>192000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>916000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>692000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1319000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2528000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1720000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1451,99 +1499,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>10788000</v>
+      </c>
+      <c r="E26" s="3">
         <v>10332000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6704000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6493000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3003000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6094000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6148000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>759000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-53000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2523000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2460000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3809000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5708000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5005000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>10792000</v>
+      </c>
+      <c r="E27" s="3">
         <v>10335000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6705000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6489000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2998000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6093000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6147000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>754000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-67000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2512000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2452000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3789000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5681000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4928000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1586,9 +1643,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1613,8 +1673,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>24</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>24</v>
@@ -1631,9 +1691,12 @@
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1676,9 +1739,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1721,99 +1787,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>123000</v>
+        <v>86000</v>
       </c>
       <c r="E32" s="3">
-        <v>358000</v>
+        <v>122000</v>
       </c>
       <c r="F32" s="3">
-        <v>264000</v>
+        <v>357000</v>
       </c>
       <c r="G32" s="3">
+        <v>265000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-121000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-13000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-75000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-178000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>518000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-161000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-322000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>34000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-132000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>27000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10792000</v>
+      </c>
+      <c r="E33" s="3">
         <v>10335000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6705000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6489000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2998000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6093000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6147000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>754000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-67000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2512000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2452000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3789000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5681000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4928000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1856,104 +1931,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10792000</v>
+      </c>
+      <c r="E35" s="3">
         <v>10335000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6705000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6489000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2998000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6093000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6147000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>754000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-67000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2512000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2452000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3789000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5681000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4928000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1971,8 +2055,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1990,68 +2075,72 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6165000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6106000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6042000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8428000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8822000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7299000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6968000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7381000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7168000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6460000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7341000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6081000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5490000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3057000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>1900000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>964000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2061,8 +2150,8 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>24</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>24</v>
@@ -2070,108 +2159,117 @@
       <c r="M42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N42" s="3">
+      <c r="N42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O42" s="3">
         <v>14000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>29000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>22000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9520000</v>
+      </c>
+      <c r="E43" s="3">
         <v>9556000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9103000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8664000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7178000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8484000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8714000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7376000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14441000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15668000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16726000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>17089000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8831000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>25599000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16827000</v>
+      </c>
+      <c r="E44" s="3">
         <v>16565000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>16270000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14038000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11402000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11266000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11529000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>10018000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8614000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9700000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12205000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12625000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>15547000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>14544000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2184,84 +2282,90 @@
       <c r="F45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="3">
         <v>119000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>23000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>19000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>48000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1744000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3206000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2595000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2526000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12241000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12631000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>45682000</v>
+      </c>
+      <c r="E46" s="3">
         <v>46949000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>43785000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>43455000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>39464000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>39193000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38603000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>36244000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>31967000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>33508000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>38867000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>38335000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>42138000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>37900000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2274,11 +2378,11 @@
       <c r="F47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="3">
         <v>4000</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>24</v>
@@ -2286,117 +2390,126 @@
       <c r="J47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="3">
         <v>14830000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>14980000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>16175000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>17868000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>30753000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>26037000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10123000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9250000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8750000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8797000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8912000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9230000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9085000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9823000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15322000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32180000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16577000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34150000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16461000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14395000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5640000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5872000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6046000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7366000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7702000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7761000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8114000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8289000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8369000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9436000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9770000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10552000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10958000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10912000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2439,9 +2552,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2484,54 +2600,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4831000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4883000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4195000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3677000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3462000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2812000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>962000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>950000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4216000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6326000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3292000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2463000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4005000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4516000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2574,54 +2696,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>87764000</v>
+      </c>
+      <c r="E54" s="3">
         <v>87476000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>81943000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>82793000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78324000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78453000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>78509000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>76962000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>74704000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>78342000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>84681000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>84896000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>88970000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>81218000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2639,8 +2767,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2658,278 +2787,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7675000</v>
+      </c>
+      <c r="E57" s="3">
         <v>7906000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8689000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8154000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6128000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5957000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7051000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6487000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4614000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5023000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6515000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6560000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6753000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8161000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11201000</v>
+      </c>
+      <c r="E58" s="3">
         <v>13553000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11430000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11914000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11332000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11574000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11593000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11033000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13965000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12844000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11501000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11031000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12391000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9648000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5762000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5554000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5019000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3779000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3561000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3757000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3735000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3657000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7553000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11491000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9861000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9706000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10271000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16344000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32272000</v>
+      </c>
+      <c r="E60" s="3">
         <v>34728000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31531000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29847000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25717000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26621000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28218000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26931000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26132000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26242000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27877000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27297000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29415000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28357000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9023000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9006000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9926000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10230000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10206000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9602000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8005000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7929000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22818000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25169000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27784000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>26719000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27752000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>24944000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3576000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3334000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3251000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3909000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3065000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2981000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3319000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3657000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12541000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12046000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12194000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13031000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14221000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18098000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2972,9 +3120,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3017,9 +3168,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3062,54 +3216,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>68270000</v>
+      </c>
+      <c r="E66" s="3">
         <v>67973000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>66052000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>66277000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>62946000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>63824000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>64429000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>63196000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>61567000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>63533000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67935000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>64085000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>71438000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>68335000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3127,8 +3287,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3171,9 +3332,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3216,9 +3380,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3261,9 +3428,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3306,54 +3476,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>59352000</v>
+      </c>
+      <c r="E72" s="3">
         <v>51250000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>43514000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>39282000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>35167000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>34437000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>30427000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26301000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27377000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>29246000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>33887000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>31854000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>29558000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>25219000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3396,9 +3572,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3441,9 +3620,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3486,54 +3668,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19491000</v>
+      </c>
+      <c r="E76" s="3">
         <v>19494000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15869000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16484000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15331000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14588000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14039000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13697000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13137000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14809000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16746000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20811000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17532000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12883000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3576,104 +3764,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10792000</v>
+      </c>
+      <c r="E81" s="3">
         <v>10335000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6705000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6489000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2998000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6093000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6147000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>754000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-67000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2512000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2452000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3789000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5681000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4928000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3691,53 +3888,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1851000</v>
+        <v>1907000</v>
       </c>
       <c r="E83" s="3">
+        <v>1926000</v>
+      </c>
+      <c r="F83" s="3">
         <v>1935000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2050000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2121000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2253000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2435000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2554000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3034000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3046000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3163000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3087000</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2527000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3780,9 +3981,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3825,9 +4029,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3870,9 +4077,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3915,9 +4125,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3960,54 +4173,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12035000</v>
+      </c>
+      <c r="E89" s="3">
         <v>12885000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7766000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7198000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6327000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6912000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6558000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5706000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5639000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6699000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8057000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10191000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5184000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6957000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4025,53 +4244,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3215000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3092000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2599000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2472000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2115000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2669000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2916000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2336000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2928000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3261000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3379000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4446000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5076000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3924000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4114,9 +4337,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4159,54 +4385,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2453000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5871000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2541000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3084000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1485000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1928000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3212000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-966000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1780000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3517000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3627000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5046000</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11427000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4224,53 +4456,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2646000</v>
+      </c>
+      <c r="E96" s="3">
         <v>2563000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2440000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2332000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2243000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2132000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1951000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1831000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1799000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1757000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1620000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1111000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1617000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1159000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4313,9 +4549,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4358,9 +4597,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4403,142 +4645,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9565000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6932000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7281000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4188000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3755000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4538000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3650000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3657000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3894000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2996000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4511000</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4019000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-106000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-110000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-194000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-29000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-13000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-44000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-126000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>38000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-28000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-169000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-174000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-43000</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-84000</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-89000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-28000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2250000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-103000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1074000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>402000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-430000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1121000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>688000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-881000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1260000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>591000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2433000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-535000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CAT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CAT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>CAT</t>
   </si>
@@ -656,222 +656,234 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>67589000</v>
+      </c>
+      <c r="E8" s="3">
         <v>64809000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>67060000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>59427000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>50971000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>41748000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>53800000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>54722000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>45462000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>38537000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>47011000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>55184000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>55656000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>65875000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>60138000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>44752000</v>
+      </c>
+      <c r="E9" s="3">
         <v>40199000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>42767000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>41350000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>35513000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>29082000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36630000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>36997000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>31260000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>27782000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>33284000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>80485000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>41455000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>47851000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>44402000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>19462000</v>
+      </c>
+      <c r="E10" s="3">
         <v>21088000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21275000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>15565000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13189000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10127000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14462000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>14903000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11824000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10755000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13727000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-25301000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14201000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18024000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>15736000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -890,56 +902,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2148000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2107000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2108000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1814000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1686000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1415000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1693000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1850000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1842000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1853000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2119000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2380000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2046000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2466000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2297000</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -985,87 +1001,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E14" s="3">
         <v>202000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>660000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1066000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-104000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>303000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>41000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>206000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>891000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1614000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1551000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>430000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>242000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>676000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>117000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>2083000</v>
+        <v>2197000</v>
       </c>
       <c r="E15" s="3">
+        <v>2153000</v>
+      </c>
+      <c r="F15" s="3">
         <v>2144000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2219000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2352000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2432000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2577000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2766000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2877000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1081,9 +1103,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1099,104 +1124,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>55825000</v>
+      </c>
+      <c r="E17" s="3">
         <v>51246000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>53392000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>49671000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>42697000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>36913000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>45687000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46386000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>39886000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>37375000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43226000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>51870000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>50029000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>57304000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>52990000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>11764000</v>
+      </c>
+      <c r="E18" s="3">
         <v>13563000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>13668000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9756000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8274000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4835000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8113000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8336000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5576000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1162000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3785000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3314000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5627000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8571000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7148000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1215,248 +1247,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-99000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-86000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-122000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-357000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-265000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>121000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>13000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>75000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>178000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-518000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>161000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>322000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-34000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>132000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-27000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>15732000</v>
+        <v>14060000</v>
       </c>
       <c r="E21" s="3">
+        <v>15802000</v>
+      </c>
+      <c r="F21" s="3">
         <v>15934000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12332000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10891000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7146000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10677000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11027000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8275000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3678000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6992000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6799000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8680000</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9648000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>502000</v>
+      </c>
+      <c r="E22" s="3">
         <v>512000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>511000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>443000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>488000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>514000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>421000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>404000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>531000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>505000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>507000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>484000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>465000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>467000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>396000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>11650000</v>
+      </c>
+      <c r="E23" s="3">
         <v>13417000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13113000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8771000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8235000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4009000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7840000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7846000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4098000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>139000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3439000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3152000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5128000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8236000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6725000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2768000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2629000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2781000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2067000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1742000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1006000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1746000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1698000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3339000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>192000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>916000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>692000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1319000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2528000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1720000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1502,105 +1550,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>8882000</v>
+      </c>
+      <c r="E26" s="3">
         <v>10788000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10332000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6704000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6493000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3003000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6094000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6148000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>759000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-53000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2523000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2460000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3809000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5708000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5005000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>8884000</v>
+      </c>
+      <c r="E27" s="3">
         <v>10792000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10335000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6705000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6489000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2998000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6093000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6147000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>754000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-67000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2512000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2452000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3789000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5681000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4928000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1646,9 +1703,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1676,8 +1736,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -1694,9 +1754,12 @@
       <c r="Q29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1742,9 +1805,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1790,105 +1856,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E32" s="3">
         <v>86000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>122000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>357000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>265000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-121000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-13000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-75000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-178000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>518000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-161000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-322000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>34000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-132000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>27000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8884000</v>
+      </c>
+      <c r="E33" s="3">
         <v>10792000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10335000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6705000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6489000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2998000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6093000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6147000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>754000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-67000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2512000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2452000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3789000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5681000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4928000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1934,110 +2009,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8884000</v>
+      </c>
+      <c r="E35" s="3">
         <v>10792000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10335000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6705000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6489000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2998000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6093000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6147000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>754000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-67000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2512000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2452000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3789000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5681000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4928000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2056,8 +2140,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2076,56 +2161,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9333000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6165000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6106000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6042000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8428000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8822000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7299000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6968000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7381000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7168000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6460000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7341000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6081000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5490000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3057000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2133,17 +2222,17 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>1900000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>964000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -2153,8 +2242,8 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>24</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>24</v>
@@ -2162,114 +2251,123 @@
       <c r="N42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O42" s="3">
+      <c r="O42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P42" s="3">
         <v>14000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>29000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>22000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11217000</v>
+      </c>
+      <c r="E43" s="3">
         <v>9520000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9556000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9103000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8664000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7178000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8484000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8714000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7376000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14441000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15668000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16726000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>17089000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8831000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>25599000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18135000</v>
+      </c>
+      <c r="E44" s="3">
         <v>16827000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>16565000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16270000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14038000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11402000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11266000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11529000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10018000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8614000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9700000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12205000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>12625000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>15547000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>14544000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2285,87 +2383,93 @@
       <c r="G45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="3">
         <v>119000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>19000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1744000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3206000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2595000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2526000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12241000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12631000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52485000</v>
+      </c>
+      <c r="E46" s="3">
         <v>45682000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>46949000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>43785000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>43455000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>39464000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>39193000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>38603000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36244000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>31967000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>33508000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>38867000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>38335000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>42138000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>37900000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2381,11 +2485,11 @@
       <c r="G47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="3">
         <v>4000</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>24</v>
@@ -2393,123 +2497,132 @@
       <c r="K47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M47" s="3">
         <v>14830000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>14980000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>16175000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>17868000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>30753000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>26037000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15848000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10123000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9250000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8750000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8797000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8912000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9230000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9085000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9823000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15322000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32180000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16577000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34150000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16461000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14395000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5562000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5640000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5872000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6046000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7366000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7702000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7761000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8114000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8289000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8369000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9436000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9770000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10552000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10958000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10912000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2555,9 +2668,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2603,57 +2719,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5519000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4831000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4883000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4195000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3677000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3462000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2812000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>962000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>950000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4216000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6326000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3292000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2463000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4005000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4516000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2699,57 +2821,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>98585000</v>
+      </c>
+      <c r="E54" s="3">
         <v>87764000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>87476000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>81943000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>82793000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78324000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>78453000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>78509000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>76962000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74704000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>78342000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>84681000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>84896000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>88970000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>81218000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2768,8 +2896,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2788,296 +2917,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8968000</v>
+      </c>
+      <c r="E57" s="3">
         <v>7675000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7906000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8689000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8154000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6128000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5957000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7051000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6487000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4614000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5023000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6515000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6560000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6753000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8161000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12792000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11201000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13553000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11430000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11914000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11332000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11574000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11593000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11033000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13965000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12844000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11501000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11031000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12391000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9648000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6654000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5762000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5554000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5019000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3779000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3561000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3757000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3735000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3657000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7553000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11491000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9861000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9706000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10271000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16344000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36558000</v>
+      </c>
+      <c r="E60" s="3">
         <v>32272000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34728000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>31531000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29847000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25717000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26621000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28218000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26931000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26132000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26242000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27877000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27297000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29415000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>28357000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11248000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9023000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9006000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9926000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10230000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10206000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9602000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8005000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7929000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22818000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>25169000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27784000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>26719000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27752000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>24944000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3747000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3576000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3334000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3251000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3909000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3065000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2981000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3319000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3657000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12541000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12046000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12194000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13031000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14221000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18098000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3123,9 +3271,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3171,9 +3322,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3219,57 +3373,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>77267000</v>
+      </c>
+      <c r="E66" s="3">
         <v>68270000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>67973000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>66052000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>66277000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>62946000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>63824000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>64429000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>63196000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>61567000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>63533000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67935000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>64085000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>71438000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>68335000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3288,8 +3448,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3335,9 +3496,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3383,9 +3547,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3431,9 +3598,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3479,57 +3649,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>65448000</v>
+      </c>
+      <c r="E72" s="3">
         <v>59352000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>51250000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>43514000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>39282000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>35167000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>34437000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>30427000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>26301000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27377000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>29246000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>33887000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>31854000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>29558000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>25219000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3575,9 +3751,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3623,9 +3802,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3671,57 +3853,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21318000</v>
+      </c>
+      <c r="E76" s="3">
         <v>19491000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19494000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15869000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16484000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15331000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14588000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14039000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13697000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13137000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14809000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16746000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20811000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17532000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12883000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3767,110 +3955,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8884000</v>
+      </c>
+      <c r="E81" s="3">
         <v>10792000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10335000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6705000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6489000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2998000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6093000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6147000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>754000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-67000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2512000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2452000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3789000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5681000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4928000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3889,56 +4086,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1907000</v>
+        <v>2028000</v>
       </c>
       <c r="E83" s="3">
+        <v>1977000</v>
+      </c>
+      <c r="F83" s="3">
         <v>1926000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1935000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2050000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2121000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2253000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2435000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2554000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3034000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3046000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3163000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3087000</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2527000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3984,9 +4185,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4032,9 +4236,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4080,9 +4287,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4128,9 +4338,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4176,57 +4389,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11739000</v>
+      </c>
+      <c r="E89" s="3">
         <v>12035000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12885000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7766000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7198000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6327000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6912000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6558000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5706000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5639000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6699000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8057000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10191000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5184000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6957000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4245,56 +4464,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4286000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3215000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3092000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2599000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2472000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2115000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2669000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2916000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2336000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2928000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3261000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3379000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4446000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5076000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3924000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4340,9 +4563,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4388,57 +4614,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4707000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2453000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5871000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2541000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3084000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1485000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1928000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3212000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-966000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1780000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3517000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3627000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5046000</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11427000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4457,56 +4689,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2749000</v>
+      </c>
+      <c r="E96" s="3">
         <v>2646000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2563000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2440000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2332000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2243000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2132000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1951000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1831000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1799000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1757000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1620000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1111000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1617000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1159000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4552,9 +4788,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4600,9 +4839,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4648,151 +4890,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3899000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9565000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6932000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7281000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4188000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3755000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4538000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3650000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3657000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3894000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2996000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4511000</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4019000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-106000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-110000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-194000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-29000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-13000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-44000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-126000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>38000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-28000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-169000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-174000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-43000</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-84000</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3090000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-89000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-28000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2250000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-103000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1074000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>402000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-430000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1121000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>688000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-881000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1260000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>591000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2433000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-535000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
